--- a/data/trans_orig/P1408-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>77866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113063</t>
+          <t>113460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78451</t>
+          <t>78301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131510</t>
+          <t>132156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178103</t>
+          <t>179186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>918660</t>
+          <t>918263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>954866</t>
+          <t>953857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1236662</t>
+          <t>1236812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1269103</t>
+          <t>1267550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2168732</t>
+          <t>2167649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2215325</t>
+          <t>2214679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36285</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>47136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77798</t>
+          <t>78243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1643494</t>
+          <t>1644149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1668540</t>
+          <t>1667983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1551388</t>
+          <t>1551284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1571432</t>
+          <t>1571556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3203288</t>
+          <t>3202843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3234450</t>
+          <t>3233950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537454</t>
+          <t>536835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>548424</t>
+          <t>547979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463253</t>
+          <t>463896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474463</t>
+          <t>474488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1005131</t>
+          <t>1005397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1020910</t>
+          <t>1020894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115329</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158816</t>
+          <t>157978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>73793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258465</t>
+          <t>259841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3117727</t>
+          <t>3118565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3161214</t>
+          <t>3163106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3268165</t>
+          <t>3266525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3304214</t>
+          <t>3305404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6397276</t>
+          <t>6395900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6455372</t>
+          <t>6457275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64093</t>
+          <t>65911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>43156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>66485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100696</t>
+          <t>99740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>910550</t>
+          <t>908732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>937860</t>
+          <t>936917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293758</t>
+          <t>1293458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315294</t>
+          <t>1315361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2210561</t>
+          <t>2211517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2246574</t>
+          <t>2244772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>36853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18751</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50762</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1924389</t>
+          <t>1927104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1950214</t>
+          <t>1949861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1735841</t>
+          <t>1736363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1749735</t>
+          <t>1749503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3667787</t>
+          <t>3667525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3696026</t>
+          <t>3695729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3022,97 +3022,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4866</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>960</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4911</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4839</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453720</t>
+          <t>453765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934011</t>
+          <t>934974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>93576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,77 +3380,77 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42468</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30954</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58197</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>116121</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>95473</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>139918</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42468</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30050</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>57023</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>116121</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>93335</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>140201</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3326346</t>
+          <t>3326206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3362675</t>
+          <t>3361981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,74 +3493,74 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3507369</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3491640</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3518883</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6387</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6853498</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6829701</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6874146</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3507369</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3492814</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3519787</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6387</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6853498</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6829418</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6876284</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>97,99%</t>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47164</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>36507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74808</t>
+          <t>75273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>707183</t>
+          <t>706989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729712</t>
+          <t>729478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>958368</t>
+          <t>958153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>978395</t>
+          <t>978545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1674199</t>
+          <t>1673734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1704737</t>
+          <t>1703672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33460</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2034138</t>
+          <t>2036074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2056796</t>
+          <t>2057283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1960381</t>
+          <t>1960859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1977902</t>
+          <t>1978617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4004013</t>
+          <t>4004455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4031225</t>
+          <t>4031305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535977</t>
+          <t>537042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545993</t>
+          <t>545991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540822</t>
+          <t>540893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548157</t>
+          <t>548156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1080729</t>
+          <t>1081027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093153</t>
+          <t>1093233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50855</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82333</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60158</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90545</t>
+          <t>91225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134656</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3295285</t>
+          <t>3291986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3326763</t>
+          <t>3326275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3471942</t>
+          <t>3472056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499559</t>
+          <t>3500277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6775062</t>
+          <t>6774523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6819173</t>
+          <t>6818493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>60341</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>75135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105522</t>
+          <t>105750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453229</t>
+          <t>453601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475768</t>
+          <t>477065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699443</t>
+          <t>698864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>716777</t>
+          <t>717251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1158693</t>
+          <t>1158465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1187222</t>
+          <t>1189080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>40993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>56884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52602</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2248319</t>
+          <t>2247539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2269424</t>
+          <t>2269586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2178864</t>
+          <t>2179193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2208739</t>
+          <t>2209102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,17 +6063,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4455321</t>
+          <t>4455322</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4437134</t>
+          <t>4431762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4472007</t>
+          <t>4470528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524609</t>
+          <t>4524610</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524609</t>
+          <t>4524610</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524609</t>
+          <t>4524610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634878</t>
+          <t>634714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643417</t>
+          <t>643210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647894</t>
+          <t>647432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656486</t>
+          <t>656652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286310</t>
+          <t>1286257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298600</t>
+          <t>1298303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101931</t>
+          <t>100192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>108220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145578</t>
+          <t>143673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198414</t>
+          <t>198782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3347166</t>
+          <t>3348905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3384704</t>
+          <t>3386265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3539981</t>
+          <t>3538273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3576184</t>
+          <t>3577390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6897177</t>
+          <t>6896809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6950013</t>
+          <t>6951918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1408-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77866</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>113793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47563</t>
+          <t>47814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78301</t>
+          <t>78263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132156</t>
+          <t>132168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179186</t>
+          <t>177933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>918263</t>
+          <t>917930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>953857</t>
+          <t>955296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1236812</t>
+          <t>1236850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1267550</t>
+          <t>1267299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2167649</t>
+          <t>2168902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2214679</t>
+          <t>2214667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>50243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>77062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1644149</t>
+          <t>1643170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1667983</t>
+          <t>1667596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1551284</t>
+          <t>1552149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1571556</t>
+          <t>1571350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3202843</t>
+          <t>3204024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3233950</t>
+          <t>3233900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536835</t>
+          <t>538093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>547979</t>
+          <t>548450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463896</t>
+          <t>463238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474488</t>
+          <t>474468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1005397</t>
+          <t>1006032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1020894</t>
+          <t>1021032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157978</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>257911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3118565</t>
+          <t>3114563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3163106</t>
+          <t>3160416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3266525</t>
+          <t>3268383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3305404</t>
+          <t>3304841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6395900</t>
+          <t>6397830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6457275</t>
+          <t>6456306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65911</t>
+          <t>64967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43156</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66485</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99740</t>
+          <t>100696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>908732</t>
+          <t>909676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>936917</t>
+          <t>938126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293458</t>
+          <t>1291638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315361</t>
+          <t>1314535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2211517</t>
+          <t>2210561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2244772</t>
+          <t>2246125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36853</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51024</t>
+          <t>49514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927104</t>
+          <t>1927319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1949861</t>
+          <t>1950055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1736363</t>
+          <t>1736099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1749503</t>
+          <t>1750427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3667525</t>
+          <t>3669035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3695729</t>
+          <t>3696706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453765</t>
+          <t>453466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934974</t>
+          <t>934714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57801</t>
+          <t>57101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93576</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58197</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95473</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139918</t>
+          <t>139935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3326206</t>
+          <t>3326417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3361981</t>
+          <t>3362681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3491640</t>
+          <t>3492749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3518883</t>
+          <t>3519915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6829701</t>
+          <t>6829684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6874146</t>
+          <t>6875480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>45233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75273</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706989</t>
+          <t>706783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729478</t>
+          <t>730049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>958153</t>
+          <t>958816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>978545</t>
+          <t>979399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1673734</t>
+          <t>1673789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1703672</t>
+          <t>1703774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>40377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2036074</t>
+          <t>2036008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2057283</t>
+          <t>2057206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1960859</t>
+          <t>1960448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1978617</t>
+          <t>1977924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4004455</t>
+          <t>4003537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4031305</t>
+          <t>4031236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537042</t>
+          <t>535446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545991</t>
+          <t>545995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540893</t>
+          <t>540927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548156</t>
+          <t>548155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1081027</t>
+          <t>1080460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093233</t>
+          <t>1093207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>51151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>84308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60044</t>
+          <t>59873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91225</t>
+          <t>91898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135195</t>
+          <t>135976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3291986</t>
+          <t>3293310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3326275</t>
+          <t>3326467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3472056</t>
+          <t>3472227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3500277</t>
+          <t>3499849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6774523</t>
+          <t>6773742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6818493</t>
+          <t>6817820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>50446</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36877</t>
+          <t>38923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>44398</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51409</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89531</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>78532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105750</t>
+          <t>109388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>466060</t>
+          <t>527096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453601</t>
+          <t>514598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477065</t>
+          <t>538619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>708624</t>
+          <t>773805</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>698864</t>
+          <t>764063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>717251</t>
+          <t>782887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1174684</t>
+          <t>1300900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1158465</t>
+          <t>1286357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1189080</t>
+          <t>1317213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>750273</t>
+          <t>818203</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>750273</t>
+          <t>818203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>750273</t>
+          <t>818203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264215</t>
+          <t>1395745</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264215</t>
+          <t>1395745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264215</t>
+          <t>1395745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26975</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56884</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69288</t>
+          <t>76629</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54082</t>
+          <t>62483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>97948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2259243</t>
+          <t>2195764</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2247539</t>
+          <t>2184220</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2269586</t>
+          <t>2204582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2196078</t>
+          <t>2125862</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2179193</t>
+          <t>2110427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2209102</t>
+          <t>2137927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4455322</t>
+          <t>4321627</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4431762</t>
+          <t>4300308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4470528</t>
+          <t>4335773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524610</t>
+          <t>4398256</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524610</t>
+          <t>4398256</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524610</t>
+          <t>4398256</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,67 +6223,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7629</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13036</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6922</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12711</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6336,69 +6336,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640103</t>
+          <t>704875</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634714</t>
+          <t>699566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643210</t>
+          <t>708121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>725857</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>720450</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>729611</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>653221</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>647432</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>656652</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1661</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1293323</t>
+          <t>1430732</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286257</t>
+          <t>1423331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298303</t>
+          <t>1436292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>72619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100192</t>
+          <t>106812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69103</t>
+          <t>80722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108220</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143673</t>
+          <t>162624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198782</t>
+          <t>210565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3365405</t>
+          <t>3427734</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3348905</t>
+          <t>3410917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3386265</t>
+          <t>3445110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3557923</t>
+          <t>3625525</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3538273</t>
+          <t>3606813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3577390</t>
+          <t>3640623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6923329</t>
+          <t>7053259</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6896809</t>
+          <t>7028509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6951918</t>
+          <t>7076450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449097</t>
+          <t>3517729</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3646493</t>
+          <t>3721345</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3646493</t>
+          <t>3721345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3646493</t>
+          <t>3721345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095591</t>
+          <t>7239074</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095591</t>
+          <t>7239074</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095591</t>
+          <t>7239074</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
